--- a/public/documentation/assessment/ETL/Claims/Alteryx/Workflow_03/Workflow_03_Assessment.xlsx
+++ b/public/documentation/assessment/ETL/Claims/Alteryx/Workflow_03/Workflow_03_Assessment.xlsx
@@ -4,9 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Workflow Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="Pipeline Stages &amp; Tools" sheetId="2" r:id="rId2"/>
-    <sheet name="Input Connections" sheetId="3" r:id="rId3"/>
-    <sheet name="Output Targets" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -400,11 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Attribute</v>
+        <v>Property</v>
       </c>
       <c r="B1" t="str">
         <v>Value</v>
@@ -412,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pipeline Name</v>
+        <v>Workflow Name</v>
       </c>
       <c r="B2" t="str">
         <v>Workflow_03</v>
@@ -420,15 +417,15 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Domain</v>
+        <v>Canonical ID</v>
       </c>
       <c r="B3" t="str">
-        <v>ETL / Data Engineering</v>
+        <v>c11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Technology Engine</v>
+        <v>Technology</v>
       </c>
       <c r="B4" t="str">
         <v>Alteryx</v>
@@ -444,358 +441,71 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Pipeline Owner</v>
+        <v>Complexity</v>
       </c>
       <c r="B6" t="str">
-        <v>Mass Mutual</v>
+        <v>High</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Execution Schedule</v>
+        <v>Criticality</v>
       </c>
       <c r="B7" t="str">
-        <v>Nightly at 01:30 AM EST</v>
+        <v>High</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Average Runtime</v>
+        <v>Schedule</v>
       </c>
       <c r="B8" t="str">
-        <v>22 mins 10 secs</v>
+        <v>Monthly (End of Month)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Input Sources Count</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
+        <v>Runtime</v>
+      </c>
+      <c r="B9" t="str">
+        <v>26s</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Output Targets Count</v>
+        <v>Tools Discovered</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Pipeline Description</v>
-      </c>
-      <c r="B11" t="str">
+        <v>Input Sources</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Output Targets</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Description</v>
+      </c>
+      <c r="B13" t="str">
         <v>Consolidates policy, claims and payment data from multiple sources.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Stage #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Tool ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tool Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Configuration Details</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Validation Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>t1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Input Data (x5)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Input</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Multi-source ingestion stream</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Valid</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>t2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Multiple Joins</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Join</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Relational join graph across Policy, Claims, Payment</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Valid</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>t3</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Filter &amp; Impute</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Preparation</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Impute missing reserve estimations</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Valid</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>t4</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Output Data (x3)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Output</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Target distribution feeds</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Valid</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Input #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Source File / Table</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Source Location</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Verification Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Policy_Extract.csv</v>
-      </c>
-      <c r="C2" t="str">
-        <v>CSV File</v>
-      </c>
-      <c r="D2" t="str">
-        <v>./Data/Policy_Extract.csv</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Claims_Master.xlsx</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Excel File</v>
-      </c>
-      <c r="D3" t="str">
-        <v>./Data/Claims_Master.xlsx</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Payment_Ledger.csv</v>
-      </c>
-      <c r="C4" t="str">
-        <v>CSV File</v>
-      </c>
-      <c r="D4" t="str">
-        <v>./Data/Payment_Ledger.csv</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Agent_Master.xlsx</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Excel File</v>
-      </c>
-      <c r="D5" t="str">
-        <v>./Data/Agent_Master.xlsx</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Customer_Demographics.parquet</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Parquet File</v>
-      </c>
-      <c r="D6" t="str">
-        <v>./Data/Customer_Demographics.parquet</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Output #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Target Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Target Location</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Downstream Consumer</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Integrated_Insurance_Cube.yxdb</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Alteryx DB</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Outputs/Integrated_Insurance_Cube.yxdb</v>
-      </c>
-      <c r="E2" t="str">
-        <v>BI Dashboards / Curated Lake</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Claims_Financial_Audit.xlsx</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Excel File</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Outputs/Claims_Financial_Audit.xlsx</v>
-      </c>
-      <c r="E3" t="str">
-        <v>BI Dashboards / Curated Lake</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Downstream_ETL_Trigger.json</v>
-      </c>
-      <c r="C4" t="str">
-        <v>JSON File</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Kafka://topic/claims_curated</v>
-      </c>
-      <c r="E4" t="str">
-        <v>BI Dashboards / Curated Lake</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>